--- a/MATERIAL_IN_OUT/Template/Export_Scraplist.xlsx
+++ b/MATERIAL_IN_OUT/Template/Export_Scraplist.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>MONTHLY SCRAP LIST</t>
   </si>
@@ -59,13 +59,13 @@
     <t>Month :</t>
   </si>
   <si>
-    <t>03</t>
+    <t>05</t>
   </si>
   <si>
     <t xml:space="preserve">Section : </t>
   </si>
   <si>
-    <t>IT</t>
+    <t>PUS</t>
   </si>
   <si>
     <t>No.</t>
@@ -273,43 +273,49 @@
     <t>(34)</t>
   </si>
   <si>
-    <t>V501</t>
+    <t>VR01</t>
   </si>
   <si>
-    <t>2020</t>
+    <t>1H99</t>
   </si>
   <si>
-    <t>1GZB10</t>
+    <t>MA6100</t>
   </si>
   <si>
-    <t>Namecost_costcentor</t>
+    <t>PUS_Door Phone</t>
   </si>
   <si>
-    <t>K1KY03A00030</t>
+    <t>PNLPWD618R1YA-V4</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>PANASONIC COMUNICATIONS PHILIPPINES CORPORATION</t>
+    <t>TSB VIETNAM CO LTD</t>
   </si>
   <si>
-    <t>123456test</t>
+    <t>IAF20447</t>
   </si>
   <si>
-    <t>Bat buoc</t>
+    <t>Claim Scrap Halb/VE055/PUSVR26-3160</t>
   </si>
   <si>
-    <t>5.1DispositionHalb</t>
+    <t>6.Claim Scrap Halb</t>
   </si>
   <si>
-    <t>201</t>
+    <t>205</t>
   </si>
   <si>
     <t>Halb</t>
   </si>
   <si>
-    <t>VA005</t>
+    <t>VE055</t>
+  </si>
+  <si>
+    <t>1AP1LPMWD505K1TA</t>
+  </si>
+  <si>
+    <t>PNLPMGE20H1YA-V4</t>
   </si>
 </sst>
 </file>
@@ -1721,19 +1727,19 @@
         <v>77</v>
       </c>
       <c r="G12" s="74">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H12" s="75">
-        <v>120000</v>
+        <v>6.44048</v>
       </c>
       <c r="I12" s="87">
-        <v>600000</v>
-      </c>
-      <c r="J12" s="75" t="s">
-        <v>78</v>
-      </c>
-      <c r="K12" s="87" t="s">
-        <v>78</v>
+        <v>57.96432</v>
+      </c>
+      <c r="J12" s="75">
+        <v>6.45348</v>
+      </c>
+      <c r="K12" s="87">
+        <v>58.08132</v>
       </c>
       <c r="L12" s="76" t="s">
         <v>78</v>
@@ -1784,34 +1790,72 @@
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="33" customFormat="1">
-      <c r="A13" s="72"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="75"/>
+      <c r="A13" s="72">
+        <v>2</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="74">
+        <v>1</v>
+      </c>
+      <c r="H13" s="75">
+        <v>17.46252</v>
+      </c>
       <c r="I13" s="87">
-        <f ref="I13:I76" t="shared" si="0">TRUNC(G13*H13,5)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="75"/>
+        <v>17.46252</v>
+      </c>
+      <c r="J13" s="75">
+        <v>17.46252</v>
+      </c>
       <c r="K13" s="87">
-        <f ref="K13:K76" t="shared" si="1">TRUNC(J13*G13,5)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="77"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="79"/>
-      <c r="S13" s="80"/>
-      <c r="T13" s="80"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
+        <v>17.46252</v>
+      </c>
+      <c r="L13" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="N13" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="O13" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="P13" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q13" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="R13" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="S13" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="T13" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="U13" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="V13" s="81" t="s">
+        <v>78</v>
+      </c>
       <c r="W13" s="71"/>
       <c r="X13" s="82"/>
       <c r="Y13" s="71"/>
@@ -1823,37 +1867,77 @@
       <c r="AE13" s="71"/>
       <c r="AF13" s="71"/>
       <c r="AG13" s="71"/>
-      <c r="AH13" s="71"/>
+      <c r="AH13" s="71" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="33" customFormat="1">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="75"/>
+      <c r="A14" s="72">
+        <v>3</v>
+      </c>
+      <c r="B14" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="74">
+        <v>1</v>
+      </c>
+      <c r="H14" s="75">
+        <v>9.54822</v>
+      </c>
       <c r="I14" s="87">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="75"/>
+        <v>9.54822</v>
+      </c>
+      <c r="J14" s="75">
+        <v>9.54822</v>
+      </c>
       <c r="K14" s="87">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="79"/>
-      <c r="S14" s="80"/>
-      <c r="T14" s="80"/>
-      <c r="U14" s="81"/>
-      <c r="V14" s="81"/>
+        <v>9.54822</v>
+      </c>
+      <c r="L14" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="N14" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="O14" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="P14" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q14" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="R14" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="T14" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="U14" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="V14" s="81" t="s">
+        <v>78</v>
+      </c>
       <c r="W14" s="71"/>
       <c r="X14" s="82"/>
       <c r="Y14" s="71"/>
@@ -1865,7 +1949,9 @@
       <c r="AE14" s="71"/>
       <c r="AF14" s="71"/>
       <c r="AG14" s="71"/>
-      <c r="AH14" s="71"/>
+      <c r="AH14" s="71" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="33" customFormat="1">
       <c r="A15" s="72"/>
@@ -1877,12 +1963,12 @@
       <c r="G15" s="74"/>
       <c r="H15" s="75"/>
       <c r="I15" s="87">
-        <f t="shared" si="0"/>
+        <f ref="I15:I76" t="shared" si="0">TRUNC(G15*H15,5)</f>
         <v>0</v>
       </c>
       <c r="J15" s="75"/>
       <c r="K15" s="87">
-        <f t="shared" si="1"/>
+        <f ref="K15:K76" t="shared" si="1">TRUNC(J15*G15,5)</f>
         <v>0</v>
       </c>
       <c r="L15" s="76"/>
